--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117612562</v>
+        <v>117612517</v>
       </c>
       <c r="B29" t="n">
-        <v>57789</v>
+        <v>57303</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4081,7 +4081,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117622652</v>
+        <v>117612653</v>
       </c>
       <c r="B30" t="n">
-        <v>106109</v>
+        <v>57990</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4179,45 +4179,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blåberga, Blåberga, Nrk</t>
+          <t>Blåberga, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502061</v>
+        <v>502234</v>
       </c>
       <c r="R30" t="n">
-        <v>6543863</v>
+        <v>6543713</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4265,7 +4269,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4284,10 +4287,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117612517</v>
+        <v>117612562</v>
       </c>
       <c r="B31" t="n">
-        <v>57303</v>
+        <v>57789</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4300,16 +4303,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>102995</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4326,7 +4329,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4408,10 +4411,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117612653</v>
+        <v>117614904</v>
       </c>
       <c r="B32" t="n">
-        <v>57990</v>
+        <v>42768</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4424,33 +4427,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103055</v>
+        <v>100770</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4514,6 +4522,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4532,10 +4541,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117608675</v>
+        <v>117622652</v>
       </c>
       <c r="B33" t="n">
-        <v>57466</v>
+        <v>106109</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4544,50 +4553,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102623</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Klevet, Nrk</t>
+          <t>Blåberga, Blåberga, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502225</v>
+        <v>502061</v>
       </c>
       <c r="R33" t="n">
-        <v>6543743</v>
+        <v>6543863</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4617,39 +4622,50 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117614904</v>
+        <v>117608675</v>
       </c>
       <c r="B34" t="n">
-        <v>42768</v>
+        <v>57466</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4658,58 +4674,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100770</v>
+        <v>102623</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Blåberga, Nrk</t>
+          <t>Klevet, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>502234</v>
+        <v>502225</v>
       </c>
       <c r="R34" t="n">
-        <v>6543713</v>
+        <v>6543743</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4736,40 +4747,29 @@
           <t>2024-06-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-07</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4039,10 +4039,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117612517</v>
+        <v>117614904</v>
       </c>
       <c r="B29" t="n">
-        <v>57303</v>
+        <v>42768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4055,33 +4055,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100770</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4145,6 +4150,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4169,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117612653</v>
+        <v>117622652</v>
       </c>
       <c r="B30" t="n">
-        <v>57990</v>
+        <v>106111</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4179,49 +4185,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blåberga, Nrk</t>
+          <t>Blåberga, Blåberga, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502234</v>
+        <v>502061</v>
       </c>
       <c r="R30" t="n">
-        <v>6543713</v>
+        <v>6543863</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4269,6 +4271,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4287,10 +4290,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117612562</v>
+        <v>117612517</v>
       </c>
       <c r="B31" t="n">
-        <v>57789</v>
+        <v>57304</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4303,16 +4306,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4329,7 +4332,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4411,10 +4414,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117614904</v>
+        <v>117612562</v>
       </c>
       <c r="B32" t="n">
-        <v>42768</v>
+        <v>57790</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4427,38 +4430,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100770</v>
+        <v>102995</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4522,7 +4520,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4541,10 +4538,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117622652</v>
+        <v>117612653</v>
       </c>
       <c r="B33" t="n">
-        <v>106109</v>
+        <v>57991</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4557,45 +4554,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blåberga, Blåberga, Nrk</t>
+          <t>Blåberga, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502061</v>
+        <v>502234</v>
       </c>
       <c r="R33" t="n">
-        <v>6543863</v>
+        <v>6543713</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4643,7 +4644,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>117608675</v>
       </c>
       <c r="B34" t="n">
-        <v>57466</v>
+        <v>57467</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -5163,7 +5163,7 @@
         <v>123548198</v>
       </c>
       <c r="B38" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -5163,7 +5163,7 @@
         <v>123548198</v>
       </c>
       <c r="B38" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3666,10 +3666,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116119054</v>
+        <v>116141131</v>
       </c>
       <c r="B26" t="n">
-        <v>56231</v>
+        <v>96696</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3682,36 +3682,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208255</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3725,7 +3716,7 @@
         <v>6543713</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3749,22 +3740,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3780,22 +3771,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116141131</v>
+        <v>117349870</v>
       </c>
       <c r="B27" t="n">
-        <v>96696</v>
+        <v>57466</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3808,27 +3799,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>102623</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3866,22 +3865,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3890,7 +3889,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3909,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117349870</v>
+        <v>117396875</v>
       </c>
       <c r="B28" t="n">
-        <v>57466</v>
+        <v>29162</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3921,20 +3919,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102623</v>
+        <v>102690</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Svartpälsbi</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anthophora retusa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3947,11 +3945,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3991,22 +3994,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4015,6 +4018,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +4037,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117396875</v>
+        <v>117612562</v>
       </c>
       <c r="B29" t="n">
-        <v>29162</v>
+        <v>57790</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4049,16 +4053,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102690</v>
+        <v>102995</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartpälsbi</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthophora retusa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4071,16 +4075,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4120,7 +4119,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4130,12 +4129,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4144,7 +4143,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117612562</v>
+        <v>117608675</v>
       </c>
       <c r="B30" t="n">
-        <v>57790</v>
+        <v>57467</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4175,20 +4173,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102995</v>
+        <v>102623</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4211,17 +4209,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blåberga, Nrk</t>
+          <t>Klevet, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502234</v>
+        <v>502225</v>
       </c>
       <c r="R30" t="n">
-        <v>6543713</v>
+        <v>6543743</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4248,19 +4246,9 @@
           <t>2024-06-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4275,22 +4263,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117608675</v>
+        <v>117622652</v>
       </c>
       <c r="B31" t="n">
-        <v>57467</v>
+        <v>106111</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4299,50 +4287,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102623</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Klevet, Nrk</t>
+          <t>Blåberga, Blåberga, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502225</v>
+        <v>502061</v>
       </c>
       <c r="R31" t="n">
-        <v>6543743</v>
+        <v>6543863</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4372,915 +4356,43 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>117612517</v>
-      </c>
-      <c r="B32" t="n">
-        <v>57304</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>117612653</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57991</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>117614904</v>
-      </c>
-      <c r="B34" t="n">
-        <v>42768</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100770</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Cupido minimus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Fuessly, 1775)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>117622652</v>
-      </c>
-      <c r="B35" t="n">
-        <v>106111</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>221849</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Backtimjan</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Blåberga, Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>502061</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6543863</v>
-      </c>
-      <c r="S35" t="n">
-        <v>50</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>118677458</v>
-      </c>
-      <c r="B36" t="n">
-        <v>44523</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>201164</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sexfläckig bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Zygaena filipendulae</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>119314388</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5352</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>105947</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Större aspvedbock</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Saperda carcharias</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>123548198</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57643</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Blåberga, Nrk</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>502234</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6543713</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4518,6 +4518,130 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125194445</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Blåberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>502234</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6543713</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4642,6 +4642,127 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125372294</v>
+      </c>
+      <c r="B34" t="n">
+        <v>108903</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Blåberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>502234</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6543713</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4523,7 +4523,7 @@
         <v>125194445</v>
       </c>
       <c r="B33" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>108903</v>
+        <v>109082</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4523,12 +4523,7 @@
         <v>125194445</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,12 +4642,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4642,7 +4642,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4642,7 +4642,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4642,7 +4642,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -4642,7 +4642,7 @@
         <v>125372294</v>
       </c>
       <c r="B34" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 26865-2020 artfynd.xlsx
+++ b/artfynd/A 26865-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4753,6 +4753,135 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126162674</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5273</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100155</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre timmerman</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Acanthocinus griseus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Blåberga, Blåberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>502061</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6543863</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
